--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484100_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484100_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5055</v>
+        <v>7.7704</v>
       </c>
       <c r="E2" t="n">
-        <v>9.210100000000001</v>
+        <v>9.3348</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7047</v>
+        <v>-1.5644</v>
       </c>
       <c r="G2" t="n">
         <v>4.2659</v>
@@ -610,13 +610,13 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2409</v>
+        <v>0.0241</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.442</v>
+        <v>-0.3173</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2011</v>
+        <v>0.3414</v>
       </c>
       <c r="V2" t="n">
         <v>3.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9862</v>
+        <v>6.3073</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2466</v>
+        <v>7.3713</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2604</v>
+        <v>-1.064</v>
       </c>
       <c r="G3" t="n">
         <v>1.3626</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5152</v>
+        <v>-0.1941</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.442</v>
+        <v>-0.3173</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0732</v>
+        <v>0.1232</v>
       </c>
       <c r="V3" t="n">
         <v>3.3534</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6671</v>
+        <v>4.3833</v>
       </c>
       <c r="E4" t="n">
-        <v>5.108</v>
+        <v>4.2918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5591</v>
+        <v>0.0915</v>
       </c>
       <c r="G4" t="n">
         <v>4.1562</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4514</v>
+        <v>1.1676</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3604</v>
+        <v>0.5442</v>
       </c>
       <c r="U4" t="n">
-        <v>1.091</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9405</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1113</v>
+        <v>1.6283</v>
       </c>
       <c r="E5" t="n">
-        <v>1.865</v>
+        <v>2.9808</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7537</v>
+        <v>-1.3525</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1017</v>
+        <v>2.9222</v>
       </c>
       <c r="H5" t="n">
-        <v>3.825</v>
+        <v>4.1828</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7233</v>
+        <v>-1.2606</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7313</v>
+        <v>3.2913</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9219</v>
+        <v>3.8912</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1906</v>
+        <v>-0.5999</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6297</v>
+        <v>-0.3691</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.097</v>
+        <v>0.2916</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5327</v>
+        <v>-0.6607</v>
       </c>
       <c r="P5" t="n">
         <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7254</v>
+        <v>-0.2409</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6291</v>
+        <v>-0.4024</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3545</v>
+        <v>0.1615</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1206</v>
+        <v>-0.4579</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7384</v>
+        <v>2.0757</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8591</v>
+        <v>-2.5336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7027</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.448</v>
+        <v>1.9896</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7453</v>
+        <v>-1.3148</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9222</v>
+        <v>1.1017</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1828</v>
+        <v>3.825</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2606</v>
+        <v>-2.7233</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2913</v>
+        <v>3.7313</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8912</v>
+        <v>3.9219</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5999</v>
+        <v>-0.1906</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3691</v>
+        <v>-2.6297</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2916</v>
+        <v>-0.097</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6607</v>
+        <v>-2.5327</v>
       </c>
       <c r="P6" t="n">
         <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1665</v>
+        <v>0.289</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9352</v>
+        <v>-0.5044</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2313</v>
+        <v>0.7934</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4579</v>
+        <v>-0.1206</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0757</v>
+        <v>1.7384</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5336</v>
+        <v>-1.8591</v>
       </c>
     </row>
     <row r="7">
@@ -951,13 +951,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3604</v>
+        <v>-0.4348</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.2248</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6028</v>
+        <v>-0.21</v>
       </c>
       <c r="G7" t="n">
         <v>-1.683</v>
@@ -996,13 +996,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1438</v>
+        <v>-0.2182</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0599</v>
+        <v>-0.5271</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0839</v>
+        <v>0.3089</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1206</v>
@@ -1029,13 +1029,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3604</v>
+        <v>-0.4348</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.2248</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6028</v>
+        <v>-0.21</v>
       </c>
       <c r="G8" t="n">
         <v>-1.683</v>
@@ -1074,13 +1074,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1438</v>
+        <v>-0.2182</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0599</v>
+        <v>-0.5271</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0839</v>
+        <v>0.3089</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1206</v>
@@ -1095,7 +1095,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,73 +1107,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1862</v>
+        <v>-3.5241</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8889</v>
+        <v>-2.5332</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2973</v>
+        <v>-0.9909</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1572</v>
+        <v>-2.533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4633</v>
+        <v>-1.0134</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-1.5196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1463</v>
+        <v>-0.9575</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1061</v>
+        <v>-1.0378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>0.0803</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3035</v>
+        <v>-1.5755</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3572</v>
+        <v>0.0244</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6607</v>
+        <v>-1.6</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4884</v>
+        <v>-0.1814</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6746</v>
+        <v>-0.5838</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8138</v>
+        <v>0.4024</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5336</v>
+        <v>-1.2065</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7996</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,67 +1185,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8631</v>
+        <v>-4.0625</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7599</v>
+        <v>-2.5408</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1032</v>
+        <v>-1.5217</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.533</v>
+        <v>-0.1572</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0134</v>
+        <v>0.4633</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5196</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9575</v>
+        <v>0.1463</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0378</v>
+        <v>0.1061</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0803</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5755</v>
+        <v>-0.3035</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0244</v>
+        <v>0.3572</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6</v>
+        <v>-0.6607</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5203</v>
+        <v>0.6121</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8105</v>
+        <v>0.0227</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2901</v>
+        <v>0.5894</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2065</v>
+        <v>-2.5336</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-2.7996</v>
       </c>
     </row>
     <row r="11">
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0285</v>
+        <v>-4.5657</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2105</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8179</v>
+        <v>-3.6215</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9052</v>
@@ -1308,13 +1308,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7023</v>
+        <v>-0.2395</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5611</v>
+        <v>-0.2947</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1412</v>
+        <v>0.0552</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0162</v>
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8569</v>
+        <v>-6.1263</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5617</v>
+        <v>-4.8871</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2952</v>
+        <v>-1.2391</v>
       </c>
       <c r="G12" t="n">
         <v>-6.4327</v>
@@ -1386,13 +1386,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1213</v>
+        <v>0.6093</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8105</v>
+        <v>-0.136</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6892</v>
+        <v>0.7453</v>
       </c>
       <c r="V12" t="n">
         <v>1.0858</v>
@@ -1419,16 +1419,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6827000000000005</v>
+        <v>1.616000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9415</v>
+        <v>14.6135</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.6242</v>
+        <v>-12.9974</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5854999999999961</v>
+        <v>-0.5854999999999979</v>
       </c>
       <c r="H13" t="n">
         <v>16.0545</v>
@@ -1455,7 +1455,7 @@
         <v>-14.5097</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5872</v>
+        <v>1.587199999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.895</v>
@@ -1464,16 +1464,16 @@
         <v>14.4822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8888999999999997</v>
+        <v>1.4098</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7152</v>
+        <v>-3.0432</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8262</v>
+        <v>4.4531</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.795199999999999</v>
+        <v>-0.7951999999999997</v>
       </c>
       <c r="W13" t="n">
         <v>14.7246</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.1586</v>
+        <v>8.462199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3233</v>
+        <v>9.9354</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1647</v>
+        <v>-1.4733</v>
       </c>
       <c r="G14" t="n">
         <v>3.7988</v>
@@ -1542,13 +1542,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2001</v>
+        <v>0.1034</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2356</v>
+        <v>-0.6234</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0354</v>
+        <v>0.7268</v>
       </c>
       <c r="V14" t="n">
         <v>4.5599</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4966</v>
+        <v>8.1266</v>
       </c>
       <c r="E15" t="n">
-        <v>8.887700000000001</v>
+        <v>9.601900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3911</v>
+        <v>-1.4753</v>
       </c>
       <c r="G15" t="n">
         <v>4.5045</v>
@@ -1620,13 +1620,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6626</v>
+        <v>-0.0326</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.672</v>
+        <v>-0.9578</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0094</v>
+        <v>0.9252</v>
       </c>
       <c r="V15" t="n">
         <v>1.4724</v>
@@ -1641,7 +1641,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1653,73 +1653,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3797</v>
+        <v>-0.47</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2482</v>
+        <v>0.2284</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8685</v>
+        <v>-0.6984</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.629</v>
+        <v>-0.5309</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.0362</v>
+        <v>-3.2102</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4071</v>
+        <v>2.6792</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3142</v>
+        <v>0.9183</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7626</v>
+        <v>-1.6119</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4484</v>
+        <v>2.5302</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3148</v>
+        <v>-1.4492</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2736</v>
+        <v>-1.5983</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9588</v>
+        <v>0.149</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6002</v>
+        <v>0.1205</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8673999999999999</v>
+        <v>-0.5157</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7328</v>
+        <v>0.6362</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4085</v>
+        <v>0.3373</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6789</v>
+        <v>1.8097</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2704</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,73 +1731,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5513</v>
+        <v>-0.6126</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8471</v>
+        <v>0.2279</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2958</v>
+        <v>-0.8405</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8568</v>
+        <v>-1.629</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9928</v>
+        <v>-4.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.136</v>
+        <v>2.4071</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.66</v>
+        <v>-0.3142</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.66</v>
+        <v>-1.7626</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.4484</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1967</v>
+        <v>-1.3148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3328</v>
+        <v>-2.2736</v>
       </c>
       <c r="O17" t="n">
-        <v>0.136</v>
+        <v>0.9588</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3055</v>
+        <v>0.6079</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.187</v>
+        <v>-0.1529</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4925</v>
+        <v>0.7609</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.2704</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,67 +1809,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9062</v>
+        <v>-0.7477</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1797</v>
+        <v>-0.8471</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7265</v>
+        <v>0.0994</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5309</v>
+        <v>-0.8568</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.2102</v>
+        <v>-0.9928</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6792</v>
+        <v>0.136</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9183</v>
+        <v>-0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6119</v>
+        <v>-0.66</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5302</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4492</v>
+        <v>-0.1967</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5983</v>
+        <v>-0.3328</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>0.136</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3157</v>
+        <v>0.1091</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9238</v>
+        <v>-0.187</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6081</v>
+        <v>0.2961</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0286</v>
+        <v>-1.7887</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5007</v>
+        <v>0.6845</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5293</v>
+        <v>-2.4732</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9045</v>
@@ -1932,13 +1932,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4909</v>
+        <v>-0.2692</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.2663</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.059</v>
+        <v>-0.0029</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0118</v>
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4486</v>
+        <v>-2.6705</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8081</v>
+        <v>0.502</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2567</v>
+        <v>-3.1725</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1092</v>
@@ -2010,13 +2010,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1412</v>
+        <v>-0.0808</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1191</v>
+        <v>-0.187</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0221</v>
+        <v>0.1062</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6789</v>
@@ -2031,7 +2031,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,58 +2043,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7743</v>
+        <v>-3.4809</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.888</v>
+        <v>-0.8298</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1137</v>
+        <v>-2.6511</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4182</v>
+        <v>0.5865</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.4016</v>
+        <v>0.7407</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9834000000000001</v>
+        <v>-0.1541</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7738</v>
+        <v>2.316</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9345</v>
+        <v>1.6734</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1606</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6444</v>
+        <v>-1.7295</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4671</v>
+        <v>-0.9327</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8227</v>
+        <v>-0.7967</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2471</v>
+        <v>-0.4804</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1303</v>
+        <v>-0.17</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3774</v>
+        <v>-0.3104</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2109,7 +2109,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8252</v>
+        <v>-3.676</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0338</v>
+        <v>-2.4921</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7914</v>
+        <v>-1.1839</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5865</v>
+        <v>-3.5385</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7407</v>
+        <v>-4.7524</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1541</v>
+        <v>1.2139</v>
       </c>
       <c r="J22" t="n">
-        <v>2.316</v>
+        <v>-1.1484</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6734</v>
+        <v>-2.4788</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6425999999999999</v>
+        <v>1.3304</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7295</v>
+        <v>-2.3901</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9327</v>
+        <v>-2.2736</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7967</v>
+        <v>-0.1165</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3806</v>
+        <v>0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8247</v>
+        <v>-0.5342</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3741</v>
+        <v>-0.6177</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4506</v>
+        <v>0.0835</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,67 +2199,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1784</v>
+        <v>-3.8202</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7982</v>
+        <v>-3.99</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3803</v>
+        <v>0.1698</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5385</v>
+        <v>-2.4182</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.7524</v>
+        <v>-3.4016</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2139</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1484</v>
+        <v>-1.7738</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4788</v>
+        <v>-1.9345</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3304</v>
+        <v>0.1606</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3901</v>
+        <v>-0.6444</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.2736</v>
+        <v>-1.4671</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1165</v>
+        <v>0.8227</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0367</v>
+        <v>0.2012</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9238</v>
+        <v>-0.2323</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1129</v>
+        <v>0.4335</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W23" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="24">
@@ -2277,10 +2277,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6776999999999993</v>
+        <v>-0.6778000000000013</v>
       </c>
       <c r="E24" t="n">
-        <v>13.0212</v>
+        <v>13.0211</v>
       </c>
       <c r="F24" t="n">
         <v>-13.699</v>
@@ -2313,7 +2313,7 @@
         <v>2.1706</v>
       </c>
       <c r="P24" t="n">
-        <v>1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.8948</v>
@@ -2322,13 +2322,13 @@
         <v>12.895</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2548999999999999</v>
+        <v>-0.2551000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.9102</v>
+        <v>-3.9101</v>
       </c>
       <c r="U24" t="n">
-        <v>3.6552</v>
+        <v>3.6551</v>
       </c>
       <c r="V24" t="n">
         <v>0.6743999999999997</v>
